--- a/assets/constructions/examples/ctd_ma1.xlsx
+++ b/assets/constructions/examples/ctd_ma1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,21 +589,46 @@
           <t>ccc</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NF3.100K120.ST</t>
+          <t>HMP2.60D20XT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BRICE</t>
+          <t>FRESAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>HMP2XT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -613,26 +638,22 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" t="n">
-        <v>60</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>38</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -645,11 +666,19 @@
           <t>h6</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>HM HARD METALL</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HM HARD METALL</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -660,13 +689,13 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V2" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>38</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -680,7 +709,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2022/BRICE</t>
+          <t>2020/FRESAL Фрезы Цельные Твердосплавные</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -695,52 +724,67 @@
         <v>0</v>
       </c>
       <c r="AF2" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>747.6799999999999</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>68736.99000000001</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1C050-0300-045-XB   1620</t>
+          <t>HMP2.90D16XT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>FRESAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoroMill® Plura 1C050-XB</t>
+          <t>HMP2XT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" t="n">
-        <v>45</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HB-12</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -755,24 +799,20 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>HM HARD METALL</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>HM HARD METALL</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PVDTiAlN</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>COROMANT</t>
-        </is>
-      </c>
+          <t>AlTiN</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -780,31 +820,27 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V3" t="n">
-        <v>81.5</v>
+        <v>92</v>
       </c>
       <c r="W3" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.14</v>
-      </c>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12,2</t>
+          <t>2020/FRESAL Фрезы Цельные Твердосплавные</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -820,45 +856,74 @@
       </c>
       <c r="AF3" t="b">
         <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>493.25</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>45346.3</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7064900400</t>
+          <t>E5400120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HELION</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>90.6490</t>
+          <t>E5400</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKNS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>45</v>
+      </c>
       <c r="I4" t="n">
-        <v>3.448</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
+      </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>HB-4</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -866,17 +931,25 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MGHM</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>HELION NORM</t>
+          <t>YG STD</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -886,17 +959,17 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="V4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="W4" t="n">
-        <v>3.448</v>
+        <v>20</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -906,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2023/Helion_general_cataloge</t>
+          <t>2017 - YG1 - General catalogue</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -921,48 +994,57 @@
         <v>0</v>
       </c>
       <c r="AF4" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HMP2.60D04</t>
+          <t>9064901200</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FRESAL</t>
+          <t>HELION</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HMP2</t>
+          <t>90.6490</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
+        <v>10.345</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HB-12</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -970,27 +1052,19 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>HM HARD METALL</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>HM HARD METALL</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>HELION NORM</t>
+        </is>
+      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
@@ -998,17 +1072,17 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V5" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>10.345</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1018,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2020/FRESAL Фрезы Цельные Твердосплавные</t>
+          <t>2023/Helion_general_cataloge</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1033,46 +1107,67 @@
         <v>0</v>
       </c>
       <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>142.61</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>13110.66</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9064602000</t>
+          <t>HM END MILL Ø4 FH960W V-MAXX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HELION</t>
+          <t>VERGNANO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>90.6460</t>
+          <t>FH960W</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>45</v>
+      </c>
       <c r="I6" t="n">
-        <v>17.241</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HB-20</t>
+          <t>HB-4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1080,17 +1175,21 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>V-MAXX</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>HELION NORM</t>
+          <t>DIN 6527 L</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1100,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="W6" t="n">
-        <v>17.241</v>
+        <v>3.5</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1120,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2023/Helion_general_cataloge</t>
+          <t>2022/Vergnano-End-Mills-Catalogue-65.pdf</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1135,7 +1234,18 @@
         <v>0</v>
       </c>
       <c r="AF6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
   </sheetData>
